--- a/data/trans_bre/P19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,19</t>
+          <t>-0,66; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,65</t>
+          <t>0,3; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,88</t>
+          <t>-0,59; 1,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,26</t>
+          <t>-0,27; 1,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,87; —</t>
+          <t>-37,37; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-87,87; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 1302,3</t>
+          <t>-71,54; 936,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,05</t>
+          <t>-1,62; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,96</t>
+          <t>-1,49; 0,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,43</t>
+          <t>-1,48; 0,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,23</t>
+          <t>-1,34; 1,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 134,3</t>
+          <t>-71,8; 139,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 136,51</t>
+          <t>-68,47; 101,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,97; 76,35</t>
+          <t>-83,26; 81,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 232,0</t>
+          <t>-66,12; 268,11</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,83</t>
+          <t>-0,47; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,16</t>
+          <t>-0,26; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,32</t>
+          <t>-2,65; 0,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,11</t>
+          <t>-0,76; 1,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 486,52</t>
+          <t>-44,16; 532,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 604,84</t>
+          <t>-34,65; 637,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-91,28; 52,1</t>
+          <t>-87,79; 76,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 399,62</t>
+          <t>-62,51; 446,19</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,71</t>
+          <t>-1,38; 0,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,13</t>
+          <t>-0,89; 1,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,5</t>
+          <t>-0,07; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,87</t>
+          <t>-0,72; 0,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 97,63</t>
+          <t>-72,05; 109,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,93; 196,47</t>
+          <t>-59,79; 174,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 353,26</t>
+          <t>-13,74; 380,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 168,36</t>
+          <t>-52,06; 193,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,55</t>
+          <t>-0,59; 0,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,01</t>
+          <t>-0,15; 0,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,76</t>
+          <t>-0,5; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,71</t>
+          <t>-0,42; 0,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 69,27</t>
+          <t>-40,74; 67,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 143,19</t>
+          <t>-15,83; 135,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 85,9</t>
+          <t>-33,05; 85,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 116,68</t>
+          <t>-34,22; 124,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>135,96%</t>
+          <t>169,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,17</t>
+          <t>-0,51; 1,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,63</t>
+          <t>0,37; 2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,93</t>
+          <t>-0,66; 1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,22</t>
+          <t>-0,02; 1,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-15,39; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-37,37; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-87,87; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 936,45</t>
+          <t>-38,71; 1144,46</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,07</t>
+          <t>-1,5; 0,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,9</t>
+          <t>-1,4; 0,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,4</t>
+          <t>-1,39; 0,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,27</t>
+          <t>-1,09; 1,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 139,49</t>
+          <t>-68,99; 122,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 101,28</t>
+          <t>-66,72; 118,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 81,47</t>
+          <t>-82,99; 72,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,12; 268,11</t>
+          <t>-60,83; 208,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,82</t>
+          <t>-0,57; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,15</t>
+          <t>-0,21; 2,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,36</t>
+          <t>-2,66; 0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,15</t>
+          <t>-0,2; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 532,31</t>
+          <t>-50,11; 476,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 637,28</t>
+          <t>-30,76; 707,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-87,79; 76,84</t>
+          <t>-88,14; 67,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 446,19</t>
+          <t>-32,59; 542,77</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,74</t>
+          <t>-1,45; 0,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,16</t>
+          <t>-1,01; 1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,56</t>
+          <t>-0,29; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,93</t>
+          <t>-0,59; 0,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 109,17</t>
+          <t>-74,53; 114,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 174,8</t>
+          <t>-59,62; 200,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 380,27</t>
+          <t>-21,72; 355,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 193,07</t>
+          <t>-48,08; 245,13</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,52</t>
+          <t>-0,48; 0,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,99</t>
+          <t>-0,08; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,77</t>
+          <t>-0,47; 0,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,69</t>
+          <t>-0,12; 0,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 67,3</t>
+          <t>-34,54; 77,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 135,73</t>
+          <t>-7,82; 147,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 85,14</t>
+          <t>-31,63; 98,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 124,9</t>
+          <t>-13,8; 138,69</t>
         </is>
       </c>
     </row>
